--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469764.5482454522</v>
+        <v>469765</v>
       </c>
       <c r="R2" t="n">
-        <v>6421166.410784098</v>
+        <v>6421166</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2005-10-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469764.5482454522</v>
+        <v>469765</v>
       </c>
       <c r="R3" t="n">
-        <v>6421166.410784098</v>
+        <v>6421166</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>2005-10-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74478059</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74478059</v>
+        <v>3919109</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>102241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469765</v>
+        <v>469793</v>
       </c>
       <c r="R2" t="n">
-        <v>6421166</v>
+        <v>6421164</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-10-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7E4e 3720. SOM: Hepatica nobilis. LEG: Hans Rydberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,36 +759,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog med hassel</t>
+          <t>lövskog med hassel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>74552104</v>
       </c>
       <c r="B3" t="n">
-        <v>101762</v>
+        <v>102240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -890,6 +881,219 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5023066</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ölmstad, 900 m NV om Fågelkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>469793</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6421164</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ölmstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-10-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-10-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>lövskog med hassel</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74478059</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ölmstad, 900 m NV om Fågelkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>469765</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6421166</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ölmstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-10-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-10-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E4e 3720. SOM: Hepatica nobilis. LEG: Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövskog med hassel</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 3361-2025 artfynd.xlsx
+++ b/artfynd/A 3361-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3919109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5023066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74478059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>